--- a/exports/MAHABANK_full_report.xlsx
+++ b/exports/MAHABANK_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q75"/>
+  <dimension ref="A1:U75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>5.89</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44582.55208333334</v>
+        <v>44585.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>20.45</v>
+        <v>19.7</v>
       </c>
       <c r="I2" t="n">
         <v>20.27622685911992</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.49</v>
+        <v>-4.14</v>
       </c>
       <c r="L2" t="n">
-        <v>1.95</v>
+        <v>4.87</v>
       </c>
       <c r="M2" t="n">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="N2" t="n">
-        <v>2.78</v>
+        <v>4.89</v>
       </c>
       <c r="O2" t="n">
         <v>1.72</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,25 +626,25 @@
         <v>10.77</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44588.55208333334</v>
+        <v>44589.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>21.05</v>
+        <v>21.35</v>
       </c>
       <c r="I3" t="n">
         <v>21.27982930195827</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K3" t="n">
-        <v>-6.85</v>
+        <v>-8.380000000000001</v>
       </c>
       <c r="L3" t="n">
-        <v>8.119999999999999</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="N3" t="n">
         <v>4.21</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,28 +695,28 @@
         <v>9.800000000000001</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44603.55208333334</v>
+        <v>44606.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>19.75</v>
+        <v>19.35</v>
       </c>
       <c r="I4" t="n">
         <v>19.39294383717345</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K4" t="n">
-        <v>-7.49</v>
+        <v>-9.369999999999999</v>
       </c>
       <c r="L4" t="n">
-        <v>7.73</v>
+        <v>10.07</v>
       </c>
       <c r="M4" t="n">
-        <v>0.74</v>
+        <v>2.28</v>
       </c>
       <c r="N4" t="n">
-        <v>1.99</v>
+        <v>4.05</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>7.55</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44655.38541666666</v>
+        <v>44655.55208333334</v>
       </c>
       <c r="H5" t="n">
-        <v>17.8</v>
+        <v>18.05</v>
       </c>
       <c r="I5" t="n">
         <v>18.01523918572313</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>49</v>
+        <v>49.16666666666666</v>
       </c>
       <c r="K5" t="n">
-        <v>8.01</v>
+        <v>6.72</v>
       </c>
       <c r="L5" t="n">
         <v>1.29</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -762,22 +833,22 @@
         <v>8.91</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44685.38541666666</v>
+        <v>44685.55208333334</v>
       </c>
       <c r="H6" t="n">
-        <v>17.65</v>
+        <v>17.3</v>
       </c>
       <c r="I6" t="n">
         <v>17.51223937949182</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>29.83333333333333</v>
+        <v>30</v>
       </c>
       <c r="K6" t="n">
-        <v>-2.22</v>
+        <v>-4.16</v>
       </c>
       <c r="L6" t="n">
-        <v>2.22</v>
+        <v>5.54</v>
       </c>
       <c r="M6" t="n">
         <v>1.1</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>7.42</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44708.55208333334</v>
+        <v>44711.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>16.55</v>
+        <v>17.2</v>
       </c>
       <c r="I7" t="n">
         <v>16.69848025085837</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>23</v>
+        <v>25.83333333333333</v>
       </c>
       <c r="K7" t="n">
-        <v>4.34</v>
+        <v>0.58</v>
       </c>
       <c r="L7" t="n">
         <v>2.6</v>
@@ -840,7 +923,7 @@
         <v>1.28</v>
       </c>
       <c r="N7" t="n">
-        <v>4.18</v>
+        <v>6.04</v>
       </c>
       <c r="O7" t="n">
         <v>-2.54</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,22 +971,22 @@
         <v>8.880000000000001</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44719.38541666666</v>
+        <v>44719.55208333334</v>
       </c>
       <c r="H8" t="n">
-        <v>16.7</v>
+        <v>16.55</v>
       </c>
       <c r="I8" t="n">
         <v>16.55328821133061</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>8</v>
+        <v>8.166666666666666</v>
       </c>
       <c r="K8" t="n">
-        <v>-2.91</v>
+        <v>-3.78</v>
       </c>
       <c r="L8" t="n">
-        <v>3.49</v>
+        <v>4.36</v>
       </c>
       <c r="M8" t="n">
         <v>-0</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>6.34</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44735.55208333334</v>
+        <v>44736.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>16.15</v>
+        <v>16.3</v>
       </c>
       <c r="I9" t="n">
         <v>16.22410313512568</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>16</v>
+        <v>16.83333333333333</v>
       </c>
       <c r="K9" t="n">
-        <v>2.42</v>
+        <v>1.51</v>
       </c>
       <c r="L9" t="n">
         <v>2.11</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>7.81</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44784.38541666666</v>
+        <v>44784.55208333334</v>
       </c>
       <c r="H10" t="n">
-        <v>17</v>
+        <v>16.95</v>
       </c>
       <c r="I10" t="n">
         <v>16.99213286617389</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>48</v>
+        <v>48.16666666666666</v>
       </c>
       <c r="K10" t="n">
-        <v>4.29</v>
+        <v>3.99</v>
       </c>
       <c r="L10" t="n">
         <v>5.52</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -1047,22 +1178,22 @@
         <v>5.38</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44790.38541666666</v>
+        <v>44790.55208333334</v>
       </c>
       <c r="H11" t="n">
-        <v>17.7</v>
+        <v>17.95</v>
       </c>
       <c r="I11" t="n">
         <v>17.86250932396232</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>5.833333333333333</v>
+        <v>6</v>
       </c>
       <c r="K11" t="n">
-        <v>-4.42</v>
+        <v>-5.9</v>
       </c>
       <c r="L11" t="n">
-        <v>4.42</v>
+        <v>6.49</v>
       </c>
       <c r="M11" t="n">
         <v>1.16</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S11" t="b">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>5.78</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44825.55208333334</v>
+        <v>44826.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>18.6</v>
+        <v>18.45</v>
       </c>
       <c r="I12" t="n">
         <v>18.56235098992931</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>35</v>
+        <v>35.83333333333334</v>
       </c>
       <c r="K12" t="n">
-        <v>3.62</v>
+        <v>2.79</v>
       </c>
       <c r="L12" t="n">
         <v>5.01</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -1161,22 +1316,22 @@
         <v>7.63</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44851.38541666666</v>
+        <v>44851.55208333334</v>
       </c>
       <c r="H13" t="n">
-        <v>18.6</v>
+        <v>18.95</v>
       </c>
       <c r="I13" t="n">
         <v>18.73417143928277</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>25</v>
+        <v>25.16666666666667</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-2.71</v>
       </c>
       <c r="L13" t="n">
-        <v>2.17</v>
+        <v>2.98</v>
       </c>
       <c r="M13" t="n">
         <v>2.56</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>6.71</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44916.55208333334</v>
+        <v>44917.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>30.25</v>
+        <v>28.9</v>
       </c>
       <c r="I14" t="n">
         <v>29.65043279791635</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>65</v>
+        <v>65.83333333333333</v>
       </c>
       <c r="K14" t="n">
-        <v>59.63</v>
+        <v>52.51</v>
       </c>
       <c r="L14" t="n">
         <v>1.85</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>90</v>
+        <v>91</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -1275,22 +1454,22 @@
         <v>26.07</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44929.38541666666</v>
+        <v>44929.55208333334</v>
       </c>
       <c r="H15" t="n">
-        <v>31.3</v>
+        <v>32.35</v>
       </c>
       <c r="I15" t="n">
         <v>31.96264283145228</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>12</v>
+        <v>12.16666666666667</v>
       </c>
       <c r="K15" t="n">
-        <v>-8.300000000000001</v>
+        <v>-11.94</v>
       </c>
       <c r="L15" t="n">
-        <v>11.07</v>
+        <v>11.94</v>
       </c>
       <c r="M15" t="n">
         <v>3.8</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>14.05</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44950.38541666666</v>
+        <v>44950.55208333334</v>
       </c>
       <c r="H16" t="n">
-        <v>30</v>
+        <v>29.3</v>
       </c>
       <c r="I16" t="n">
         <v>29.84846396833577</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>20.83333333333333</v>
+        <v>21</v>
       </c>
       <c r="K16" t="n">
-        <v>-7.26</v>
+        <v>-9.43</v>
       </c>
       <c r="L16" t="n">
         <v>10.36</v>
@@ -1362,7 +1553,19 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>10.32</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>44987.55208333334</v>
+        <v>44988.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>26.1</v>
+        <v>27.45</v>
       </c>
       <c r="I17" t="n">
         <v>26.89078047571334</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>37</v>
+        <v>37.83333333333334</v>
       </c>
       <c r="K17" t="n">
-        <v>10.92</v>
+        <v>6.31</v>
       </c>
       <c r="L17" t="n">
         <v>5.8</v>
@@ -1410,7 +1613,7 @@
         <v>6</v>
       </c>
       <c r="N17" t="n">
-        <v>4.48</v>
+        <v>6.32</v>
       </c>
       <c r="O17" t="n">
         <v>-4.4</v>
@@ -1419,7 +1622,19 @@
         <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -1446,22 +1661,22 @@
         <v>9.51</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>44998.38541666666</v>
+        <v>44998.55208333334</v>
       </c>
       <c r="H18" t="n">
-        <v>26.1</v>
+        <v>25.5</v>
       </c>
       <c r="I18" t="n">
         <v>25.91639162738249</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>10</v>
+        <v>10.16666666666667</v>
       </c>
       <c r="K18" t="n">
-        <v>-4.92</v>
+        <v>-7.1</v>
       </c>
       <c r="L18" t="n">
-        <v>4.92</v>
+        <v>7.47</v>
       </c>
       <c r="M18" t="n">
         <v>1.49</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S18" t="b">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>9.039999999999999</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45016.55208333334</v>
+        <v>45019.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>24.7</v>
+        <v>25.3</v>
       </c>
       <c r="I19" t="n">
         <v>24.94698452131837</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>18</v>
+        <v>20.83333333333333</v>
       </c>
       <c r="K19" t="n">
-        <v>3.14</v>
+        <v>0.78</v>
       </c>
       <c r="L19" t="n">
         <v>2.94</v>
@@ -1533,7 +1760,19 @@
         <v>1</v>
       </c>
       <c r="Q19" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>9.15</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45069.55208333334</v>
+        <v>45070.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>30.1</v>
+        <v>29.45</v>
       </c>
       <c r="I20" t="n">
         <v>29.60375218184017</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>50.16666666666666</v>
+        <v>51</v>
       </c>
       <c r="K20" t="n">
-        <v>18.97</v>
+        <v>16.4</v>
       </c>
       <c r="L20" t="n">
         <v>2.37</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,28 +1868,28 @@
         <v>7.34</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45077.55208333334</v>
+        <v>45078.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>30.4</v>
+        <v>31.45</v>
       </c>
       <c r="I21" t="n">
         <v>30.60548788673067</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K21" t="n">
-        <v>-3.23</v>
+        <v>-6.79</v>
       </c>
       <c r="L21" t="n">
-        <v>3.57</v>
+        <v>7.3</v>
       </c>
       <c r="M21" t="n">
         <v>1.2</v>
       </c>
       <c r="N21" t="n">
-        <v>3.05</v>
+        <v>3.29</v>
       </c>
       <c r="O21" t="n">
         <v>-2.49</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,28 +1937,28 @@
         <v>7.26</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45085.55208333334</v>
+        <v>45086.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>30.4</v>
+        <v>28.4</v>
       </c>
       <c r="I22" t="n">
         <v>29.85634167559577</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K22" t="n">
-        <v>-3.34</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="L22" t="n">
-        <v>4.45</v>
+        <v>10.33</v>
       </c>
       <c r="M22" t="n">
-        <v>0.33</v>
+        <v>1.32</v>
       </c>
       <c r="N22" t="n">
-        <v>2.54</v>
+        <v>6.58</v>
       </c>
       <c r="O22" t="n">
         <v>3.29</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S22" t="b">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>10.32</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45105.38541666666</v>
+        <v>45105.55208333334</v>
       </c>
       <c r="H23" t="n">
-        <v>28.05</v>
+        <v>28.45</v>
       </c>
       <c r="I23" t="n">
         <v>28.31827356720513</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>19</v>
+        <v>19.16666666666667</v>
       </c>
       <c r="K23" t="n">
-        <v>1.23</v>
+        <v>-0.18</v>
       </c>
       <c r="L23" t="n">
         <v>5.63</v>
@@ -1761,7 +2036,19 @@
         <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S23" t="b">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>6.08</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45218.55208333334</v>
+        <v>45219.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>45.75</v>
+        <v>44.2</v>
       </c>
       <c r="I24" t="n">
         <v>45.00955830858575</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>113</v>
+        <v>113.8333333333333</v>
       </c>
       <c r="K24" t="n">
-        <v>60.81</v>
+        <v>55.36</v>
       </c>
       <c r="L24" t="n">
         <v>2.11</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>155</v>
+        <v>156</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>4</v>
+      </c>
+      <c r="U24" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>10.08</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45242.76041666666</v>
+        <v>45243.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>43.45</v>
+        <v>45.1</v>
       </c>
       <c r="I25" t="n">
         <v>44.7132949526387</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>23.375</v>
+        <v>24</v>
       </c>
       <c r="K25" t="n">
-        <v>1.7</v>
+        <v>-2.04</v>
       </c>
       <c r="L25" t="n">
         <v>4.75</v>
@@ -1866,7 +2165,7 @@
         <v>1.33</v>
       </c>
       <c r="N25" t="n">
-        <v>3.52</v>
+        <v>5.87</v>
       </c>
       <c r="O25" t="n">
         <v>-4.26</v>
@@ -1875,7 +2174,19 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>8.210000000000001</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45253.38541666666</v>
+        <v>45253.55208333334</v>
       </c>
       <c r="H26" t="n">
-        <v>43.85</v>
+        <v>43.45</v>
       </c>
       <c r="I26" t="n">
         <v>43.56817416781933</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>10</v>
+        <v>10.16666666666667</v>
       </c>
       <c r="K26" t="n">
-        <v>-2.77</v>
+        <v>-3.66</v>
       </c>
       <c r="L26" t="n">
         <v>4.88</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S26" t="b">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1959,28 +2282,28 @@
         <v>5.24</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45261.55208333334</v>
+        <v>45264.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>44.15</v>
+        <v>45.7</v>
       </c>
       <c r="I27" t="n">
         <v>45.25276010255274</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>8</v>
+        <v>10.83333333333333</v>
       </c>
       <c r="K27" t="n">
-        <v>-1.61</v>
+        <v>-5.18</v>
       </c>
       <c r="L27" t="n">
-        <v>4.49</v>
+        <v>6.67</v>
       </c>
       <c r="M27" t="n">
-        <v>0.68</v>
+        <v>3.4</v>
       </c>
       <c r="N27" t="n">
-        <v>2.08</v>
+        <v>3.85</v>
       </c>
       <c r="O27" t="n">
         <v>-0.57</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,22 +2351,22 @@
         <v>5.8</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45280.38541666666</v>
+        <v>45280.55208333334</v>
       </c>
       <c r="H28" t="n">
-        <v>46.9</v>
+        <v>44.75</v>
       </c>
       <c r="I28" t="n">
         <v>45.24988303970622</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>16</v>
+        <v>16.16666666666667</v>
       </c>
       <c r="K28" t="n">
-        <v>2.63</v>
+        <v>-2.08</v>
       </c>
       <c r="L28" t="n">
-        <v>1.09</v>
+        <v>3.39</v>
       </c>
       <c r="M28" t="n">
         <v>0.11</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S28" t="b">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2073,28 +2420,28 @@
         <v>9.859999999999999</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45302.55208333334</v>
+        <v>45303.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>46.1</v>
+        <v>48.4</v>
       </c>
       <c r="I29" t="n">
         <v>47.53157226045985</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>22</v>
+        <v>22.83333333333333</v>
       </c>
       <c r="K29" t="n">
-        <v>-3.02</v>
+        <v>-8.16</v>
       </c>
       <c r="L29" t="n">
-        <v>6.7</v>
+        <v>8.27</v>
       </c>
       <c r="M29" t="n">
         <v>1.21</v>
       </c>
       <c r="N29" t="n">
-        <v>3.85</v>
+        <v>4.77</v>
       </c>
       <c r="O29" t="n">
         <v>-6.48</v>
@@ -2103,7 +2450,19 @@
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>7.83</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45331.55208333334</v>
+        <v>45334.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>61.5</v>
+        <v>57</v>
       </c>
       <c r="I30" t="n">
         <v>57.65306788033837</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>31</v>
       </c>
       <c r="K30" t="n">
-        <v>27.07</v>
+        <v>17.77</v>
       </c>
       <c r="L30" t="n">
         <v>4.75</v>
@@ -2151,7 +2510,7 @@
         <v>0.2</v>
       </c>
       <c r="N30" t="n">
-        <v>5.81</v>
+        <v>9.84</v>
       </c>
       <c r="O30" t="n">
         <v>4.77</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -2187,22 +2558,22 @@
         <v>21.71</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45356.38541666666</v>
+        <v>45356.55208333334</v>
       </c>
       <c r="H31" t="n">
-        <v>62.9</v>
+        <v>63.7</v>
       </c>
       <c r="I31" t="n">
         <v>63.10661285457299</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>22</v>
+        <v>22.16666666666667</v>
       </c>
       <c r="K31" t="n">
-        <v>-10.35</v>
+        <v>-11.75</v>
       </c>
       <c r="L31" t="n">
-        <v>11.67</v>
+        <v>12.28</v>
       </c>
       <c r="M31" t="n">
         <v>0.96</v>
@@ -2217,7 +2588,19 @@
         <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,28 +2627,28 @@
         <v>7.92</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45362.55208333334</v>
+        <v>45363.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>61.25</v>
+        <v>58.45</v>
       </c>
       <c r="I32" t="n">
         <v>58.65453479465759</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>6</v>
+        <v>6.833333333333333</v>
       </c>
       <c r="K32" t="n">
-        <v>-3.85</v>
+        <v>-8.24</v>
       </c>
       <c r="L32" t="n">
-        <v>4.16</v>
+        <v>8.56</v>
       </c>
       <c r="M32" t="n">
         <v>-0</v>
       </c>
       <c r="N32" t="n">
-        <v>2.35</v>
+        <v>4.08</v>
       </c>
       <c r="O32" t="n">
         <v>4.08</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S32" t="b">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -2301,22 +2696,22 @@
         <v>12</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45378.55208333334</v>
+        <v>45379.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>59.3</v>
+        <v>62.65</v>
       </c>
       <c r="I33" t="n">
         <v>60.82031586753763</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K33" t="n">
-        <v>-1.45</v>
+        <v>-7.19</v>
       </c>
       <c r="L33" t="n">
-        <v>5.82</v>
+        <v>7.27</v>
       </c>
       <c r="M33" t="n">
         <v>0.85</v>
@@ -2331,7 +2726,19 @@
         <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S33" t="b">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2358,22 +2765,22 @@
         <v>10.7</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45400.55208333334</v>
+        <v>45401.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>61.8</v>
+        <v>61.5</v>
       </c>
       <c r="I34" t="n">
         <v>61.65077853011154</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K34" t="n">
-        <v>-1.36</v>
+        <v>-1.84</v>
       </c>
       <c r="L34" t="n">
-        <v>5.35</v>
+        <v>5.51</v>
       </c>
       <c r="M34" t="n">
         <v>3.23</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S34" t="b">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -2415,22 +2834,22 @@
         <v>6.36</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45408.38541666666</v>
+        <v>45408.55208333334</v>
       </c>
       <c r="H35" t="n">
-        <v>65.40000000000001</v>
+        <v>67.75</v>
       </c>
       <c r="I35" t="n">
         <v>65.40966539833488</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>7</v>
+        <v>7.166666666666667</v>
       </c>
       <c r="K35" t="n">
-        <v>-6.34</v>
+        <v>-10.16</v>
       </c>
       <c r="L35" t="n">
-        <v>8.289999999999999</v>
+        <v>12.85</v>
       </c>
       <c r="M35" t="n">
         <v>1.07</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,28 +2903,28 @@
         <v>8.17</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45418.55208333334</v>
+        <v>45419.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>66.90000000000001</v>
+        <v>64.84999999999999</v>
       </c>
       <c r="I36" t="n">
         <v>65.52289922729139</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>10</v>
+        <v>10.83333333333333</v>
       </c>
       <c r="K36" t="n">
-        <v>-1.25</v>
+        <v>-4.28</v>
       </c>
       <c r="L36" t="n">
-        <v>3.76</v>
+        <v>4.72</v>
       </c>
       <c r="M36" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="N36" t="n">
-        <v>2.26</v>
+        <v>2.69</v>
       </c>
       <c r="O36" t="n">
         <v>3.91</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S36" t="b">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -2529,22 +2972,22 @@
         <v>10.66</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45434.55208333334</v>
+        <v>45435.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>67.59999999999999</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="I37" t="n">
         <v>67.89448942057724</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K37" t="n">
-        <v>-4.24</v>
+        <v>-6.25</v>
       </c>
       <c r="L37" t="n">
-        <v>5.47</v>
+        <v>8.4</v>
       </c>
       <c r="M37" t="n">
         <v>0.78</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -2586,28 +3041,28 @@
         <v>6.26</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45446.55208333334</v>
+        <v>45447.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>72.59999999999999</v>
+        <v>64.75</v>
       </c>
       <c r="I38" t="n">
         <v>67.04387926945594</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>12</v>
       </c>
       <c r="K38" t="n">
-        <v>5.37</v>
+        <v>-6.02</v>
       </c>
       <c r="L38" t="n">
-        <v>3.48</v>
+        <v>14.37</v>
       </c>
       <c r="M38" t="n">
         <v>1.45</v>
       </c>
       <c r="N38" t="n">
-        <v>2.47</v>
+        <v>11.98</v>
       </c>
       <c r="O38" t="n">
         <v>2</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>15.46</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45485.55208333334</v>
+        <v>45488.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>65.20999999999999</v>
+        <v>67.23</v>
       </c>
       <c r="I39" t="n">
         <v>65.86876855858007</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>38.16666666666666</v>
+        <v>41</v>
       </c>
       <c r="K39" t="n">
-        <v>-0.71</v>
+        <v>-3.83</v>
       </c>
       <c r="L39" t="n">
         <v>11.2</v>
@@ -2664,7 +3131,7 @@
         <v>1.02</v>
       </c>
       <c r="N39" t="n">
-        <v>3.85</v>
+        <v>5.51</v>
       </c>
       <c r="O39" t="n">
         <v>-11.98</v>
@@ -2673,7 +3140,19 @@
         <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,22 +3179,22 @@
         <v>7.47</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45495.55208333334</v>
+        <v>45496.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>66.72</v>
+        <v>64.73999999999999</v>
       </c>
       <c r="I40" t="n">
         <v>64.77379180385303</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K40" t="n">
-        <v>-0.76</v>
+        <v>-3.7</v>
       </c>
       <c r="L40" t="n">
-        <v>3.61</v>
+        <v>6.4</v>
       </c>
       <c r="M40" t="n">
         <v>0.65</v>
@@ -2730,7 +3209,19 @@
         <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S40" t="b">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>8.9</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45548.38541666666</v>
+        <v>45548.55208333334</v>
       </c>
       <c r="H41" t="n">
-        <v>61.1</v>
+        <v>61.15</v>
       </c>
       <c r="I41" t="n">
         <v>61.14147291196755</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>52</v>
+        <v>52.16666666666666</v>
       </c>
       <c r="K41" t="n">
-        <v>5.62</v>
+        <v>5.55</v>
       </c>
       <c r="L41" t="n">
         <v>9.31</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>75</v>
+        <v>76</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>3</v>
+      </c>
+      <c r="U41" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="42">
@@ -2814,28 +3317,28 @@
         <v>4.82</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45553.55208333334</v>
+        <v>45554.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>59.21</v>
+        <v>57.89</v>
       </c>
       <c r="I42" t="n">
         <v>58.49787624717565</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>5</v>
+        <v>5.833333333333333</v>
       </c>
       <c r="K42" t="n">
-        <v>-3.17</v>
+        <v>-5.33</v>
       </c>
       <c r="L42" t="n">
-        <v>3.6</v>
+        <v>6.13</v>
       </c>
       <c r="M42" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="N42" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="O42" t="n">
         <v>4</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S42" t="b">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -2871,28 +3386,28 @@
         <v>7.3</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45555.55208333334</v>
+        <v>45558.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>59</v>
+        <v>61.62</v>
       </c>
       <c r="I43" t="n">
         <v>61.11791349989225</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>1.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K43" t="n">
-        <v>-1.92</v>
+        <v>-6.44</v>
       </c>
       <c r="L43" t="n">
-        <v>4.47</v>
+        <v>6.93</v>
       </c>
       <c r="M43" t="n">
         <v>1.33</v>
       </c>
       <c r="N43" t="n">
-        <v>1.13</v>
+        <v>7.12</v>
       </c>
       <c r="O43" t="n">
         <v>-1.47</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S43" t="b">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -2928,25 +3455,25 @@
         <v>8.08</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45566.55208333334</v>
+        <v>45568.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>59.7</v>
+        <v>58.37</v>
       </c>
       <c r="I44" t="n">
         <v>58.55710095272069</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K44" t="n">
-        <v>-3.12</v>
+        <v>-5.27</v>
       </c>
       <c r="L44" t="n">
-        <v>4.53</v>
+        <v>5.47</v>
       </c>
       <c r="M44" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.17</v>
       </c>
       <c r="N44" t="n">
         <v>2.63</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>6.69</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45595.38541666666</v>
+        <v>45595.55208333334</v>
       </c>
       <c r="H45" t="n">
-        <v>52.8</v>
+        <v>55.7</v>
       </c>
       <c r="I45" t="n">
         <v>53.25286488190861</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>27</v>
+        <v>27.16666666666667</v>
       </c>
       <c r="K45" t="n">
-        <v>9.539999999999999</v>
+        <v>4.57</v>
       </c>
       <c r="L45" t="n">
         <v>1.59</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S45" t="b">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,28 +3593,28 @@
         <v>12.15</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45608.55208333334</v>
+        <v>45609.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>52.37</v>
+        <v>51.01</v>
       </c>
       <c r="I46" t="n">
         <v>51.46790903437994</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>13</v>
+        <v>13.83333333333333</v>
       </c>
       <c r="K46" t="n">
-        <v>-5.98</v>
+        <v>-8.42</v>
       </c>
       <c r="L46" t="n">
-        <v>6.64</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="M46" t="n">
-        <v>0.65</v>
+        <v>1.66</v>
       </c>
       <c r="N46" t="n">
-        <v>2.65</v>
+        <v>3.8</v>
       </c>
       <c r="O46" t="n">
         <v>6.75</v>
@@ -3072,7 +3623,19 @@
         <v>1</v>
       </c>
       <c r="Q46" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,25 +3662,25 @@
         <v>9.44</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45618.55208333334</v>
+        <v>45621.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>52.99</v>
+        <v>54.7</v>
       </c>
       <c r="I47" t="n">
         <v>54.55529360640804</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>12</v>
       </c>
       <c r="K47" t="n">
-        <v>-3.88</v>
+        <v>-7.23</v>
       </c>
       <c r="L47" t="n">
-        <v>4.39</v>
+        <v>9.1</v>
       </c>
       <c r="M47" t="n">
-        <v>0.41</v>
+        <v>3.79</v>
       </c>
       <c r="N47" t="n">
         <v>3.31</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S47" t="b">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -3156,25 +3731,25 @@
         <v>7.48</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45638.55208333334</v>
+        <v>45639.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>55.76</v>
+        <v>55.3</v>
       </c>
       <c r="I48" t="n">
         <v>55.33614903580288</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K48" t="n">
-        <v>1.94</v>
+        <v>1.1</v>
       </c>
       <c r="L48" t="n">
         <v>1.19</v>
       </c>
       <c r="M48" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.22</v>
       </c>
       <c r="N48" t="n">
         <v>1.37</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,28 +3800,28 @@
         <v>4.92</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45659.55208333334</v>
+        <v>45660.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>52.7</v>
+        <v>55.89</v>
       </c>
       <c r="I49" t="n">
         <v>54.42887334501026</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K49" t="n">
-        <v>4.7</v>
+        <v>-1.07</v>
       </c>
       <c r="L49" t="n">
         <v>2.31</v>
       </c>
       <c r="M49" t="n">
-        <v>0.72</v>
+        <v>3.81</v>
       </c>
       <c r="N49" t="n">
-        <v>3.3</v>
+        <v>4.91</v>
       </c>
       <c r="O49" t="n">
         <v>-0.13</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,22 +3869,22 @@
         <v>7.31</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45664.38541666666</v>
+        <v>45664.55208333334</v>
       </c>
       <c r="H50" t="n">
-        <v>51.9</v>
+        <v>51.35</v>
       </c>
       <c r="I50" t="n">
         <v>51.87935105108896</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>4</v>
+        <v>4.166666666666667</v>
       </c>
       <c r="K50" t="n">
-        <v>-7.14</v>
+        <v>-8.119999999999999</v>
       </c>
       <c r="L50" t="n">
-        <v>7.34</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="M50" t="n">
         <v>0.07000000000000001</v>
@@ -3300,7 +3899,19 @@
         <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S50" t="b">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>1</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -3327,22 +3938,22 @@
         <v>7.94</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45671.38541666666</v>
+        <v>45671.55208333334</v>
       </c>
       <c r="H51" t="n">
-        <v>48.93</v>
+        <v>52.3</v>
       </c>
       <c r="I51" t="n">
         <v>50.45934352991127</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>6.833333333333333</v>
+        <v>7</v>
       </c>
       <c r="K51" t="n">
-        <v>4.71</v>
+        <v>-1.85</v>
       </c>
       <c r="L51" t="n">
-        <v>1.17</v>
+        <v>5.94</v>
       </c>
       <c r="M51" t="n">
         <v>1.51</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S51" t="b">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>11.65</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45698.55208333334</v>
+        <v>45699.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>49.19</v>
+        <v>47.88</v>
       </c>
       <c r="I52" t="n">
         <v>48.0410296670206</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>27</v>
+        <v>27.83333333333333</v>
       </c>
       <c r="K52" t="n">
-        <v>-5.95</v>
+        <v>-8.449999999999999</v>
       </c>
       <c r="L52" t="n">
         <v>8.51</v>
@@ -3405,7 +4028,7 @@
         <v>1.74</v>
       </c>
       <c r="N52" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="O52" t="n">
         <v>12.47</v>
@@ -3414,7 +4037,19 @@
         <v>1</v>
       </c>
       <c r="Q52" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>7.92</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45734.55208333334</v>
+        <v>45735.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>46</v>
+        <v>47.42</v>
       </c>
       <c r="I53" t="n">
         <v>47.34693540760824</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>35.16666666666666</v>
+        <v>36</v>
       </c>
       <c r="K53" t="n">
-        <v>3.93</v>
+        <v>0.96</v>
       </c>
       <c r="L53" t="n">
         <v>7.02</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,28 +4145,28 @@
         <v>7.85</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45751.55208333334</v>
+        <v>45754.38541666666</v>
       </c>
       <c r="H54" t="n">
-        <v>46.62</v>
+        <v>43.59</v>
       </c>
       <c r="I54" t="n">
         <v>45.936893509038</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K54" t="n">
-        <v>-1.69</v>
+        <v>-8.08</v>
       </c>
       <c r="L54" t="n">
-        <v>3.42</v>
+        <v>11.43</v>
       </c>
       <c r="M54" t="n">
-        <v>0.6899999999999999</v>
+        <v>9.91</v>
       </c>
       <c r="N54" t="n">
-        <v>3.93</v>
+        <v>5.36</v>
       </c>
       <c r="O54" t="n">
         <v>3.57</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,28 +4214,28 @@
         <v>8.85</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45762.55208333334</v>
+        <v>45763.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>46.1</v>
+        <v>47.45</v>
       </c>
       <c r="I55" t="n">
         <v>47.44833205487408</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K55" t="n">
-        <v>-5.76</v>
+        <v>-8.859999999999999</v>
       </c>
       <c r="L55" t="n">
-        <v>6.77</v>
+        <v>9.84</v>
       </c>
       <c r="M55" t="n">
         <v>2.11</v>
       </c>
       <c r="N55" t="n">
-        <v>1.77</v>
+        <v>3.19</v>
       </c>
       <c r="O55" t="n">
         <v>-5.36</v>
@@ -3585,7 +4244,19 @@
         <v>1</v>
       </c>
       <c r="Q55" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S55" t="b">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>1</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -3612,28 +4283,28 @@
         <v>7.67</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45785.55208333334</v>
+        <v>45786.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>50.45</v>
+        <v>48.3</v>
       </c>
       <c r="I56" t="n">
         <v>48.89960386813573</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>23</v>
       </c>
       <c r="K56" t="n">
-        <v>6.32</v>
+        <v>1.79</v>
       </c>
       <c r="L56" t="n">
         <v>2.91</v>
       </c>
       <c r="M56" t="n">
-        <v>1.8</v>
+        <v>5.63</v>
       </c>
       <c r="N56" t="n">
-        <v>3.51</v>
+        <v>3.67</v>
       </c>
       <c r="O56" t="n">
         <v>3.19</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,22 +4352,22 @@
         <v>7.28</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45793.55208333334</v>
+        <v>45796.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>51.01</v>
+        <v>53.63</v>
       </c>
       <c r="I57" t="n">
         <v>51.81710406064268</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>10</v>
       </c>
       <c r="K57" t="n">
-        <v>-5.61</v>
+        <v>-11.04</v>
       </c>
       <c r="L57" t="n">
-        <v>6.81</v>
+        <v>11.99</v>
       </c>
       <c r="M57" t="n">
         <v>2.88</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S57" t="b">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>1</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -3726,25 +4421,25 @@
         <v>8.01</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45820.55208333334</v>
+        <v>45821.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>54.15</v>
+        <v>53.4</v>
       </c>
       <c r="I58" t="n">
         <v>53.87975886668875</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K58" t="n">
-        <v>0.97</v>
+        <v>-0.43</v>
       </c>
       <c r="L58" t="n">
         <v>6.54</v>
       </c>
       <c r="M58" t="n">
-        <v>0.7</v>
+        <v>2.12</v>
       </c>
       <c r="N58" t="n">
         <v>3.32</v>
@@ -3756,7 +4451,19 @@
         <v>1</v>
       </c>
       <c r="Q58" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="59">
@@ -3783,28 +4490,28 @@
         <v>6.87</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45835.55208333334</v>
+        <v>45838.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>54.42</v>
+        <v>56.57</v>
       </c>
       <c r="I59" t="n">
         <v>56.41841304577285</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K59" t="n">
-        <v>-1.91</v>
+        <v>-5.94</v>
       </c>
       <c r="L59" t="n">
-        <v>5.22</v>
+        <v>7.4</v>
       </c>
       <c r="M59" t="n">
         <v>1.44</v>
       </c>
       <c r="N59" t="n">
-        <v>1.78</v>
+        <v>5.02</v>
       </c>
       <c r="O59" t="n">
         <v>0.44</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,22 +4559,22 @@
         <v>6.95</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45870.38541666666</v>
+        <v>45870.55208333334</v>
       </c>
       <c r="H60" t="n">
-        <v>55.64</v>
+        <v>54.3</v>
       </c>
       <c r="I60" t="n">
         <v>55.13910444006414</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>32</v>
+        <v>32.16666666666666</v>
       </c>
       <c r="K60" t="n">
-        <v>-1.64</v>
+        <v>-4.01</v>
       </c>
       <c r="L60" t="n">
-        <v>3.48</v>
+        <v>4.53</v>
       </c>
       <c r="M60" t="n">
         <v>0.71</v>
@@ -3870,7 +4589,19 @@
         <v>1</v>
       </c>
       <c r="Q60" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>5.4</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45910.38541666666</v>
+        <v>45910.55208333334</v>
       </c>
       <c r="H61" t="n">
-        <v>53.6</v>
+        <v>54.19</v>
       </c>
       <c r="I61" t="n">
         <v>54.01879123380618</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>39.83333333333334</v>
+        <v>40</v>
       </c>
       <c r="K61" t="n">
-        <v>1.29</v>
+        <v>0.2</v>
       </c>
       <c r="L61" t="n">
         <v>3.59</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>4.6</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45925.55208333334</v>
+        <v>45926.38541666666</v>
       </c>
       <c r="H62" t="n">
-        <v>55.44</v>
+        <v>54.19</v>
       </c>
       <c r="I62" t="n">
         <v>55.05420385450758</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>15</v>
+        <v>15.83333333333333</v>
       </c>
       <c r="K62" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="L62" t="n">
         <v>1.24</v>
@@ -3975,7 +4718,7 @@
         <v>0.58</v>
       </c>
       <c r="N62" t="n">
-        <v>1.67</v>
+        <v>2.31</v>
       </c>
       <c r="O62" t="n">
         <v>3.4</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S62" t="b">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>1</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -4011,25 +4766,25 @@
         <v>6.48</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45933.55208333334</v>
+        <v>45936.38541666666</v>
       </c>
       <c r="H63" t="n">
-        <v>56.52</v>
+        <v>57.26</v>
       </c>
       <c r="I63" t="n">
         <v>56.77523758897039</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>10</v>
       </c>
       <c r="K63" t="n">
-        <v>-4.3</v>
+        <v>-5.67</v>
       </c>
       <c r="L63" t="n">
-        <v>5.37</v>
+        <v>6.29</v>
       </c>
       <c r="M63" t="n">
-        <v>0.38</v>
+        <v>0.76</v>
       </c>
       <c r="N63" t="n">
         <v>1.74</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>5.5</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45993.38541666666</v>
+        <v>45993.55208333334</v>
       </c>
       <c r="H64" t="n">
-        <v>57.78</v>
+        <v>57.5</v>
       </c>
       <c r="I64" t="n">
         <v>57.63352915360287</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>57</v>
+        <v>57.16666666666666</v>
       </c>
       <c r="K64" t="n">
-        <v>0.91</v>
+        <v>0.42</v>
       </c>
       <c r="L64" t="n">
         <v>4.54</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>78</v>
+        <v>79</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>3</v>
+      </c>
+      <c r="U64" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="65">
@@ -4125,28 +4904,28 @@
         <v>6.4</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46020.55208333334</v>
+        <v>46021.38541666666</v>
       </c>
       <c r="H65" t="n">
-        <v>57.81</v>
+        <v>59</v>
       </c>
       <c r="I65" t="n">
         <v>58.46569388764464</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>27</v>
+        <v>27.83333333333333</v>
       </c>
       <c r="K65" t="n">
-        <v>-0.54</v>
+        <v>-2.61</v>
       </c>
       <c r="L65" t="n">
-        <v>1.2</v>
+        <v>2.85</v>
       </c>
       <c r="M65" t="n">
         <v>0.62</v>
       </c>
       <c r="N65" t="n">
-        <v>1.47</v>
+        <v>4.74</v>
       </c>
       <c r="O65" t="n">
         <v>-0.35</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S65" t="b">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>1</v>
+      </c>
+      <c r="U65" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -4182,28 +4973,28 @@
         <v>5.02</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46052.55208333334</v>
+        <v>46054.38541666666</v>
       </c>
       <c r="H66" t="n">
-        <v>65.5</v>
+        <v>62.07</v>
       </c>
       <c r="I66" t="n">
         <v>63.13913928496478</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>31.16666666666667</v>
+        <v>33</v>
       </c>
       <c r="K66" t="n">
-        <v>11.02</v>
+        <v>5.2</v>
       </c>
       <c r="L66" t="n">
         <v>2.9</v>
       </c>
       <c r="M66" t="n">
-        <v>1.08</v>
+        <v>1.53</v>
       </c>
       <c r="N66" t="n">
-        <v>4.13</v>
+        <v>6.87</v>
       </c>
       <c r="O66" t="n">
         <v>4.74</v>
@@ -4212,7 +5003,19 @@
         <v>1</v>
       </c>
       <c r="Q66" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>2</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -4239,22 +5042,22 @@
         <v>9.16</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46062.55208333334</v>
+        <v>46063.38541666666</v>
       </c>
       <c r="H67" t="n">
-        <v>66.15000000000001</v>
+        <v>67.3</v>
       </c>
       <c r="I67" t="n">
         <v>67.07053259551174</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K67" t="n">
-        <v>-6.57</v>
+        <v>-8.43</v>
       </c>
       <c r="L67" t="n">
-        <v>8.65</v>
+        <v>9.07</v>
       </c>
       <c r="M67" t="n">
         <v>3.9</v>
@@ -4269,7 +5072,19 @@
         <v>1</v>
       </c>
       <c r="Q67" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S67" t="b">
+        <v>0</v>
+      </c>
+      <c r="T67" t="n">
+        <v>1</v>
+      </c>
+      <c r="U67" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -4296,19 +5111,19 @@
         <v>7.87</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46083.55208333334</v>
+        <v>46085.38541666666</v>
       </c>
       <c r="H68" t="n">
-        <v>72.16</v>
+        <v>68.06</v>
       </c>
       <c r="I68" t="n">
         <v>70.18098709618032</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K68" t="n">
-        <v>7.22</v>
+        <v>1.13</v>
       </c>
       <c r="L68" t="n">
         <v>4.52</v>
@@ -4317,7 +5132,7 @@
         <v>5.35</v>
       </c>
       <c r="N68" t="n">
-        <v>3.32</v>
+        <v>5.28</v>
       </c>
       <c r="O68" t="n">
         <v>1.44</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>2</v>
+      </c>
+      <c r="U68" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -4353,25 +5180,25 @@
         <v>10.87</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46119.55208333334</v>
+        <v>46120.38541666666</v>
       </c>
       <c r="H69" t="n">
-        <v>66.55</v>
+        <v>70.04000000000001</v>
       </c>
       <c r="I69" t="n">
         <v>67.33972358913795</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>34.16666666666666</v>
+        <v>35</v>
       </c>
       <c r="K69" t="n">
-        <v>2.22</v>
+        <v>-2.91</v>
       </c>
       <c r="L69" t="n">
         <v>5.66</v>
       </c>
       <c r="M69" t="n">
-        <v>4.42</v>
+        <v>4.43</v>
       </c>
       <c r="N69" t="n">
         <v>5.73</v>
@@ -4383,7 +5210,19 @@
         <v>1</v>
       </c>
       <c r="Q69" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>2</v>
+      </c>
+      <c r="U69" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -4410,19 +5249,19 @@
         <v>10</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46153.55208333334</v>
+        <v>46154.38541666666</v>
       </c>
       <c r="H70" t="n">
-        <v>81.84999999999999</v>
+        <v>79.7</v>
       </c>
       <c r="I70" t="n">
         <v>79.92312721442137</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>33.16666666666666</v>
+        <v>34</v>
       </c>
       <c r="K70" t="n">
-        <v>16.86</v>
+        <v>13.79</v>
       </c>
       <c r="L70" t="n">
         <v>3.17</v>
@@ -4431,7 +5270,7 @@
         <v>3.45</v>
       </c>
       <c r="N70" t="n">
-        <v>2.79</v>
+        <v>4.02</v>
       </c>
       <c r="O70" t="n">
         <v>5.62</v>
@@ -4440,7 +5279,19 @@
         <v>1</v>
       </c>
       <c r="Q70" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>2</v>
+      </c>
+      <c r="U70" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -4467,28 +5318,28 @@
         <v>9.41</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>46181.55208333334</v>
+        <v>46182.38541666666</v>
       </c>
       <c r="H71" t="n">
-        <v>79.40000000000001</v>
+        <v>83.26000000000001</v>
       </c>
       <c r="I71" t="n">
         <v>81.26949815089252</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>27.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K71" t="n">
-        <v>0.38</v>
+        <v>-4.47</v>
       </c>
       <c r="L71" t="n">
-        <v>3.45</v>
+        <v>4.83</v>
       </c>
       <c r="M71" t="n">
         <v>1.52</v>
       </c>
       <c r="N71" t="n">
-        <v>1.88</v>
+        <v>5.81</v>
       </c>
       <c r="O71" t="n">
         <v>-4.02</v>
@@ -4497,7 +5348,19 @@
         <v>1</v>
       </c>
       <c r="Q71" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>2</v>
+      </c>
+      <c r="U71" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -4524,19 +5387,19 @@
         <v>8.34</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>46209.55208333334</v>
+        <v>46210.38541666666</v>
       </c>
       <c r="H72" t="n">
-        <v>86.48</v>
+        <v>83.43000000000001</v>
       </c>
       <c r="I72" t="n">
         <v>86.19543980219676</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>27.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K72" t="n">
-        <v>3.87</v>
+        <v>0.2</v>
       </c>
       <c r="L72" t="n">
         <v>4.4</v>
@@ -4545,7 +5408,7 @@
         <v>0.61</v>
       </c>
       <c r="N72" t="n">
-        <v>2.5</v>
+        <v>3.89</v>
       </c>
       <c r="O72" t="n">
         <v>5.81</v>
@@ -4554,7 +5417,19 @@
         <v>1</v>
       </c>
       <c r="Q72" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S72" t="b">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
+        <v>2</v>
+      </c>
+      <c r="U72" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -4581,19 +5456,19 @@
         <v>9.5</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>46245.55208333334</v>
+        <v>46246.38541666666</v>
       </c>
       <c r="H73" t="n">
-        <v>79</v>
+        <v>81.31999999999999</v>
       </c>
       <c r="I73" t="n">
         <v>81.14152897251994</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>35.16666666666666</v>
+        <v>36</v>
       </c>
       <c r="K73" t="n">
-        <v>5.31</v>
+        <v>2.53</v>
       </c>
       <c r="L73" t="n">
         <v>4.83</v>
@@ -4602,7 +5477,7 @@
         <v>1.29</v>
       </c>
       <c r="N73" t="n">
-        <v>2.42</v>
+        <v>3.67</v>
       </c>
       <c r="O73" t="n">
         <v>-3.89</v>
@@ -4611,7 +5486,19 @@
         <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S73" t="b">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
+        <v>2</v>
+      </c>
+      <c r="U73" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -4638,19 +5525,19 @@
         <v>5.91</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>46280.38541666666</v>
+        <v>46280.55208333334</v>
       </c>
       <c r="H74" t="n">
-        <v>81.17</v>
+        <v>80.12</v>
       </c>
       <c r="I74" t="n">
         <v>81.07168939935502</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>34</v>
+        <v>34.16666666666666</v>
       </c>
       <c r="K74" t="n">
-        <v>-0.18</v>
+        <v>-1.48</v>
       </c>
       <c r="L74" t="n">
         <v>3.16</v>
@@ -4668,7 +5555,19 @@
         <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S74" t="b">
+        <v>1</v>
+      </c>
+      <c r="T74" t="n">
+        <v>2</v>
+      </c>
+      <c r="U74" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="75">
@@ -4719,6 +5618,14 @@
       <c r="Q75" t="n">
         <v>57</v>
       </c>
+      <c r="R75" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S75" t="b">
+        <v>1</v>
+      </c>
+      <c r="T75" t="inlineStr"/>
+      <c r="U75" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6821,7 +7728,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>22.4</v>
+        <v>23.4</v>
       </c>
     </row>
     <row r="6">
@@ -6831,7 +7738,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>19</v>
+        <v>20.8</v>
       </c>
     </row>
     <row r="7">
@@ -6841,7 +7748,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>113</v>
+        <v>113.8</v>
       </c>
     </row>
     <row r="8">
@@ -6851,7 +7758,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -6861,7 +7768,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>29.8</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10">
@@ -6871,7 +7778,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>39.5</v>
+        <v>40.8</v>
       </c>
     </row>
     <row r="11">
@@ -6881,7 +7788,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="12">
@@ -6891,7 +7798,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13">
@@ -6901,7 +7808,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>75.3</v>
+        <v>74</v>
       </c>
     </row>
     <row r="14">
@@ -6911,7 +7818,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.11</v>
+        <v>-1.12</v>
       </c>
     </row>
     <row r="15">
@@ -6921,7 +7828,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4.5</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="16">
@@ -6931,7 +7838,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.34</v>
+        <v>-3.54</v>
       </c>
     </row>
     <row r="17">
@@ -6941,7 +7848,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>60.81</v>
+        <v>55.36</v>
       </c>
     </row>
     <row r="18">
@@ -6951,7 +7858,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>45.2</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="19">
@@ -6961,7 +7868,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4.73</v>
+        <v>6.15</v>
       </c>
     </row>
     <row r="20">
@@ -6971,7 +7878,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.47</v>
+        <v>5.63</v>
       </c>
     </row>
     <row r="21">
@@ -6981,7 +7888,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>11.67</v>
+        <v>14.37</v>
       </c>
     </row>
     <row r="22">
@@ -6991,7 +7898,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>27</v>
+        <v>42</v>
       </c>
     </row>
     <row r="23">
@@ -7001,7 +7908,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24">
@@ -7011,7 +7918,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.45</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="25">
@@ -7021,7 +7928,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>6</v>
+        <v>9.91</v>
       </c>
     </row>
     <row r="26">
@@ -7031,7 +7938,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.85</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="27">
@@ -7051,7 +7958,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>26</v>
+        <v>42</v>
       </c>
     </row>
     <row r="29">
